--- a/assets/documents/tableau_synthese.xlsx
+++ b/assets/documents/tableau_synthese.xlsx
@@ -1408,7 +1408,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customFormat="1" customHeight="1" s="2">
+    <row r="8" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Réalisation en cours de formation
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H20" s="22" t="n"/>
     </row>
-    <row r="21" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="21" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -1928,7 +1928,7 @@
       <c r="G28" s="21" t="n"/>
       <c r="H28" s="22" t="n"/>
     </row>
-    <row r="29" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -2050,10 +2050,12 @@
       <c r="H37" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:H2"/>

--- a/assets/documents/tableau_synthese.xlsx
+++ b/assets/documents/tableau_synthese.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -109,6 +109,11 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="20"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -675,7 +680,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -882,6 +887,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1317,12 +1328,12 @@
           <t>Option :</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="76" t="inlineStr">
         <is>
           <t>☐ SISR</t>
         </is>
       </c>
-      <c r="H4" s="56" t="inlineStr">
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>☑ SLAM</t>
         </is>
@@ -1577,7 +1588,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="14" ht="90" customFormat="1" customHeight="1" s="2">
       <c r="A14" s="63" t="inlineStr">
         <is>
           <t>MCP-serveur - Serveur Model Context Protocol
@@ -1768,7 +1779,7 @@
       <c r="G21" s="54" t="n"/>
       <c r="H21" s="55" t="n"/>
     </row>
-    <row r="22" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="22" ht="90" customFormat="1" customHeight="1" s="2">
       <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Comparateur d'IA Automatisé (Testing_Claude_code)
@@ -1801,7 +1812,7 @@
       </c>
       <c r="H22" s="22" t="n"/>
     </row>
-    <row r="23" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="23" ht="90" customFormat="1" customHeight="1" s="2">
       <c r="A23" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
@@ -1877,7 +1888,7 @@
       <c r="G28" s="54" t="n"/>
       <c r="H28" s="55" t="n"/>
     </row>
-    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
+    <row r="29" ht="90" customFormat="1" customHeight="1" s="2">
       <c r="A29" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - AgentSea
@@ -2000,7 +2011,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="48"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="2" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/assets/documents/tableau_synthese.xlsx
+++ b/assets/documents/tableau_synthese.xlsx
@@ -1527,7 +1527,7 @@
       <c r="G11" s="65" t="n"/>
       <c r="H11" s="69" t="n"/>
     </row>
-    <row r="12" ht="115" customFormat="1" customHeight="1" s="2">
+    <row r="12" ht="20" customFormat="1" customHeight="1" s="2">
       <c r="A12" s="68" t="inlineStr">
         <is>
           <t>── 2ème année ──</t>
@@ -1541,7 +1541,7 @@
       <c r="G12" s="49" t="n"/>
       <c r="H12" s="50" t="n"/>
     </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="2">
+    <row r="13" ht="95" customFormat="1" customHeight="1" s="2">
       <c r="A13" s="70" t="inlineStr">
         <is>
           <t>LinkedIn Bot - Bot de publication automatique IA pour LinkedIn
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C13" s="64" t="n"/>
       <c r="D13" s="65" t="n"/>
-      <c r="E13" s="66" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1618,7 +1618,7 @@
           <t>01/03/26 au 30/04/26</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H15" s="22" t="n"/>
     </row>
-    <row r="16" ht="95" customFormat="1" customHeight="1" s="2">
+    <row r="16" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -1680,7 +1680,7 @@
       <c r="G17" s="74" t="n"/>
       <c r="H17" s="22" t="n"/>
     </row>
-    <row r="18" ht="30" customFormat="1" customHeight="1" s="2">
+    <row r="18" ht="95" customFormat="1" customHeight="1" s="2">
       <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
@@ -1705,7 +1705,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="115" customFormat="1" customHeight="1" s="2">
+    <row r="19" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -1719,7 +1719,7 @@
       <c r="G19" s="54" t="n"/>
       <c r="H19" s="55" t="n"/>
     </row>
-    <row r="20" ht="115" customFormat="1" customHeight="1" s="2">
+    <row r="20" ht="95" customFormat="1" customHeight="1" s="2">
       <c r="A20" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - AgentSea
@@ -1733,7 +1733,7 @@
           <t>01/05/25 au 31/07/25</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1743,7 +1743,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H20" s="22" t="n"/>
     </row>
-    <row r="21" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="21" customFormat="1" s="2">
       <c r="A21" s="78" t="n"/>
       <c r="B21" s="78" t="n"/>
       <c r="C21" s="78" t="n"/>
@@ -1770,7 +1770,7 @@
       <c r="G21" s="78" t="n"/>
       <c r="H21" s="78" t="n"/>
     </row>
-    <row r="22" ht="115" customFormat="1" customHeight="1" s="2">
+    <row r="22" customFormat="1" s="2">
       <c r="A22" s="78" t="n"/>
       <c r="B22" s="78" t="n"/>
       <c r="C22" s="78" t="n"/>
@@ -1905,17 +1905,17 @@
   <mergeCells count="14">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/documents/tableau_synthese.xlsx
+++ b/assets/documents/tableau_synthese.xlsx
@@ -1266,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col width="70.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -1606,57 +1606,81 @@
       <c r="H14" s="66" t="n"/>
     </row>
     <row r="15" ht="95" customFormat="1" customHeight="1" s="2">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>TP Linux - Commandes de base et gestion des droits
+Technos : Linux, Bash, GNU coreutils
+Docs : TP réalisé en cours (Lycée Louis Bascan)</t>
+        </is>
+      </c>
+      <c r="B15" s="71" t="inlineStr">
+        <is>
+          <t>01/01/26 au 28/02/26</t>
+        </is>
+      </c>
+      <c r="C15" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D15" s="65" t="n"/>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="69" t="n"/>
+      <c r="G15" s="69" t="n"/>
+      <c r="H15" s="66" t="n"/>
+    </row>
+    <row r="16" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>ArtisanConnect - Plateforme de mise en relation artisans/clients
 Technos : PHP, MySQL, CSS, Responsive
 Docs : Dépôt GitHub MathieuGal/Projet-Sites-Artisan</t>
         </is>
       </c>
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B16" s="73" t="inlineStr">
         <is>
           <t>01/03/26 au 30/04/26</t>
         </is>
       </c>
-      <c r="C15" s="74" t="inlineStr">
+      <c r="C16" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D15" s="74" t="inlineStr">
+      <c r="D16" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="74" t="inlineStr">
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" s="74" t="inlineStr">
+      <c r="G16" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="30" customFormat="1" customHeight="1" s="2">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="H16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de première année</t>
         </is>
       </c>
-      <c r="B16" s="54" t="n"/>
-      <c r="C16" s="54" t="n"/>
-      <c r="D16" s="54" t="n"/>
-      <c r="E16" s="54" t="n"/>
-      <c r="F16" s="54" t="n"/>
-      <c r="G16" s="54" t="n"/>
-      <c r="H16" s="55" t="n"/>
-    </row>
-    <row r="17" ht="95" customFormat="1" customHeight="1" s="2">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="55" t="n"/>
+    </row>
+    <row r="18" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Comparateur d'IA Automatisé (Testing_Claude_code)
 Framework de benchmark de LLMs en parallèle, export JSON/CSV
@@ -1664,24 +1688,24 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B18" s="73" t="inlineStr">
         <is>
           <t>01/02/25 au 30/04/25</t>
         </is>
       </c>
-      <c r="C17" s="74" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="74" t="inlineStr">
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G17" s="74" t="n"/>
-      <c r="H17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="95" customFormat="1" customHeight="1" s="2">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
 Veille tech automatisée multi-sources, parseur OPML, déduplication
@@ -1689,38 +1713,38 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B18" s="73" t="inlineStr">
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>01/06/25 au 31/08/25</t>
         </is>
       </c>
-      <c r="C18" s="74" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="75" t="inlineStr">
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="75" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customFormat="1" customHeight="1" s="2">
-      <c r="A19" s="32" t="inlineStr">
+    <row r="20" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de seconde année</t>
         </is>
       </c>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="54" t="n"/>
-      <c r="H19" s="55" t="n"/>
-    </row>
-    <row r="20" ht="95" customFormat="1" customHeight="1" s="2">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="55" t="n"/>
+    </row>
+    <row r="21" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - AgentSea
 Agents IA autonomes navigant sur le web (headless browsers, LLM-piloté)
@@ -1728,47 +1752,37 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B20" s="73" t="inlineStr">
+      <c r="B21" s="73" t="inlineStr">
         <is>
           <t>01/05/25 au 31/07/25</t>
         </is>
       </c>
-      <c r="C20" s="74" t="inlineStr">
+      <c r="C21" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" s="74" t="inlineStr">
+      <c r="D21" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E20" s="74" t="inlineStr">
+      <c r="E21" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F20" s="74" t="inlineStr">
+      <c r="F21" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G20" s="74" t="inlineStr">
+      <c r="G21" s="74" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H20" s="22" t="n"/>
-    </row>
-    <row r="21" customFormat="1" s="2">
-      <c r="A21" s="78" t="n"/>
-      <c r="B21" s="78" t="n"/>
-      <c r="C21" s="78" t="n"/>
-      <c r="D21" s="78" t="n"/>
-      <c r="E21" s="78" t="n"/>
-      <c r="F21" s="78" t="n"/>
-      <c r="G21" s="78" t="n"/>
-      <c r="H21" s="78" t="n"/>
+      <c r="H21" s="22" t="n"/>
     </row>
     <row r="22" customFormat="1" s="2">
       <c r="A22" s="78" t="n"/>
@@ -1900,23 +1914,32 @@
       <c r="G34" s="78" t="n"/>
       <c r="H34" s="78" t="n"/>
     </row>
-    <row r="35" customFormat="1" s="2"/>
+    <row r="35" customFormat="1" s="2">
+      <c r="A35" s="78" t="n"/>
+      <c r="B35" s="78" t="n"/>
+      <c r="C35" s="78" t="n"/>
+      <c r="D35" s="78" t="n"/>
+      <c r="E35" s="78" t="n"/>
+      <c r="F35" s="78" t="n"/>
+      <c r="G35" s="78" t="n"/>
+      <c r="H35" s="78" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
